--- a/MTX-CM-2026-001/MTX-PO-2026-001_Orcamento_REV15.xlsx
+++ b/MTX-CM-2026-001/MTX-PO-2026-001_Orcamento_REV15.xlsx
@@ -953,180 +953,180 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="9">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>1.9.1</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>COMP-MTX-06a</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>PF-1 · autobrocante requadro/guia U100</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="8" t="n">
         <v>831</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="8" t="n">
         <v>0.7494</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="8">
         <f>E15*F15</f>
         <v/>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>COMP-MTX</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>discriminado na R15 (era verba única) — preço unit. pro-rata provisório, validar com suprimentos</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="9">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>1.9.2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>COMP-MTX-06b</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>PF-2 · autobrocante fixação painel PIR/requadro</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="8" t="n">
         <v>928</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="8" t="n">
         <v>0.7494</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="8">
         <f>E16*F16</f>
         <v/>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>COMP-MTX</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>discriminado na R15 — preço unit. pro-rata provisório, validar com suprimentos</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="9">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>1.9.3</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>COMP-MTX-06c</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>PF-3 · autobrocante junção/chapa de espera CHP</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="8" t="n">
         <v>152</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="8" t="n">
         <v>0.7494</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="8">
         <f>E17*F17</f>
         <v/>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>COMP-MTX</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>corrigido na R13 (era 206) — discriminado na R15</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="9">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>1.9.4</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>COMP-MTX-06d</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>PF-J · parafuso de junção estrutural JP</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="8" t="n">
         <v>0.7494</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="8">
         <f>E18*F18</f>
         <v/>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>COMP-MTX</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>discriminado na R15 — preço unit. pro-rata provisório, validar com suprimentos</t>
         </is>
@@ -5558,7 +5558,6 @@
         <v/>
       </c>
     </row>
-    <row r="140"/>
     <row r="141">
       <c r="A141" s="16" t="inlineStr">
         <is>
@@ -6836,28 +6835,28 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Item 1.9 discriminado em 1.9.1 (PF-1, 831un), 1.9.2 (PF-2, 928un), 1.9.3 (PF-3, 152un), 1.9.4 (PF-J, 24un).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Preço unitário usado: R$ 0.7494/un, pro-rata do valor de verba original (R$ 1450 / 1935 un) — NÃO é cotação nova, é estimativa provisória.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PENDÊNCIA: total oficial do kit (~2.760 un, README R14) excede em ~825 un o subtotal discriminável (1.935 un) — diferença (inclui "PF-1M campo") sem preço nem quantidade rastreada em nenhuma planilha de origem.</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>[RECONCILIADO EM 07/07/2026] O gap de ~825 un foi explicado: PF-4, PF-5, PF-1M e itens de cimenticia/capuz (ver Romaneio_Fabricacao_R15.xlsx aba 07) nao tinham sido trazidos ao subtotal de 1.935 un. Subtotal real ~2.893 un, proximo do total README (~2.760). O preco pro-rata usado em 1.9.1-1.9.4 (R$0,7494/un) foi calculado sobre a base ANTIGA de 1.935 un — suprimentos deve recalcular sobre a base ampliada (~2.893 un) antes de validar o preco definitivo; nao alterado aqui por ser decisao de precificacao.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Nenhuma outra alteração de escopo, quantidade ou preço unitário em relação à REV.13/14.</t>
         </is>
